--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -811,703 +811,703 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9964,0.0007,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9876,0.0011,0.0026,0.0006</t>
-  </si>
-  <si>
-    <t>0.1268,0.0008,0.0001,0.9152</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9843,0.0007,0.0055,0.0002</t>
+  </si>
+  <si>
+    <t>0.0117,0.0009,0.0001,0.9968</t>
+  </si>
+  <si>
+    <t>0.9933,0.0004,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.1202,0.0002,0.0024,0.9185</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0008,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9584,0.0003,0.0433,0.0000</t>
+  </si>
+  <si>
+    <t>0.0037,0.0002,0.9960,0.0002</t>
+  </si>
+  <si>
+    <t>0.1503,0.0009,0.9114,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.0006,0.9963,0.0001</t>
+  </si>
+  <si>
+    <t>0.9235,0.0021,0.0568,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9991,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.2949,0.7518,0.0048,0.0006</t>
+  </si>
+  <si>
+    <t>0.0065,0.9931,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8668,0.0009,0.1243,0.0004</t>
+  </si>
+  <si>
+    <t>0.8699,0.0002,0.1781,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0002,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0089,0.0000,0.9956,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0000,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9997,0.0003</t>
+  </si>
+  <si>
+    <t>0.0190,0.9839,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.8704,0.0063,0.0585,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.9903,0.0329,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7755,0.2574,0.0044,0.0006</t>
+  </si>
+  <si>
+    <t>0.0043,0.9386,0.4863,0.0003</t>
+  </si>
+  <si>
+    <t>0.0033,0.8955,0.5850,0.0012</t>
+  </si>
+  <si>
+    <t>0.0026,0.0002,0.9968,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.0103,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.1083,0.0002,0.9590,0.0000</t>
+  </si>
+  <si>
+    <t>0.0196,0.1348,0.9087,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9962,0.0070,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.9787,0.0006,0.8610</t>
+  </si>
+  <si>
+    <t>0.0003,0.9976,0.0008,0.0131</t>
+  </si>
+  <si>
+    <t>0.0003,0.9985,0.0035,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9986,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0029,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.6319,0.9942,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0377,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.9965,0.0056,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9713,0.0218,0.0036,0.0014</t>
+  </si>
+  <si>
+    <t>0.9961,0.0036,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0052,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9922,0.0107,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0021,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9890,0.9891,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0069,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0056,0.9953,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9968,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0643,0.9502,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0781,0.9391,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9689,0.0019,0.0157,0.0001</t>
+  </si>
+  <si>
+    <t>0.0649,0.0011,0.9346,0.0024</t>
+  </si>
+  <si>
+    <t>0.0011,0.0250,0.9964,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.9947,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9951,0.9546,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9978,0.2711,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9962,0.9945,0.0000</t>
+  </si>
+  <si>
+    <t>0.3974,0.0013,0.2359,0.1320</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0101,0.0000,0.0000,0.9988</t>
+  </si>
+  <si>
+    <t>0.0106,0.0048,0.0046,0.9868</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.0625,0.9926</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.9980,0.3560,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.9778,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9065,0.9020,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9698,0.9327,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.8246,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.5969,0.0000</t>
+  </si>
+  <si>
+    <t>0.9958,0.0048,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9925,0.0083,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.7317,0.0007,0.3477,0.0001</t>
-  </si>
-  <si>
-    <t>0.0424,0.0072,0.9314,0.0006</t>
-  </si>
-  <si>
-    <t>0.0645,0.0001,0.9724,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.9882,0.0003,0.0049,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.9955,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.0660,0.9402,0.0075,0.0010</t>
-  </si>
-  <si>
-    <t>0.0021,0.9975,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9112,0.0002,0.1096,0.0001</t>
-  </si>
-  <si>
-    <t>0.6448,0.0006,0.4350,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0050,0.0002,0.9950,0.0001</t>
-  </si>
-  <si>
-    <t>0.1559,0.0001,0.9534,0.0000</t>
-  </si>
-  <si>
-    <t>0.0084,0.0003,0.9906,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0044,0.9959,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.7979,0.0280,0.0501,0.0012</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9997,0.0006</t>
-  </si>
-  <si>
-    <t>0.0027,0.9141,0.4109,0.0000</t>
-  </si>
-  <si>
-    <t>0.9938,0.0053,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.5999,0.0006,0.2772,0.0003</t>
-  </si>
-  <si>
-    <t>0.7796,0.2445,0.0040,0.0015</t>
-  </si>
-  <si>
-    <t>0.0086,0.9724,0.0468,0.0004</t>
-  </si>
-  <si>
-    <t>0.0026,0.8374,0.7321,0.0008</t>
-  </si>
-  <si>
-    <t>0.0180,0.0054,0.9728,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.0312,0.9956,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0007,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.5515,0.9963,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.9864,0.0106,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9995,0.0003</t>
-  </si>
-  <si>
-    <t>0.0120,0.2273,0.0009,0.9500</t>
-  </si>
-  <si>
-    <t>0.0023,0.9893,0.0138,0.0034</t>
-  </si>
-  <si>
-    <t>0.0003,0.9971,0.0085,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9989,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0012,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0929,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0036,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0020,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.9928,0.0079,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9954,0.0025,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9937,0.0045,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0012,0.9993,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0019,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9752,0.9799,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0112,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0127,0.0055,0.9836,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0275,0.9724,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9987,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9315,0.0010,0.0738,0.0001</t>
-  </si>
-  <si>
-    <t>0.0573,0.0014,0.9497,0.0012</t>
-  </si>
-  <si>
-    <t>0.0016,0.0228,0.9940,0.0016</t>
-  </si>
-  <si>
-    <t>0.0000,0.9977,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9971,0.2209,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9965,0.4047,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.9832,0.0000</t>
-  </si>
-  <si>
-    <t>0.0279,0.0003,0.2688,0.8070</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0073,0.0001,0.0000,0.9990</t>
-  </si>
-  <si>
-    <t>0.0023,0.0004,0.0030,0.9969</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0050,0.9994</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.9992,0.0150,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9941,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9314,0.9852,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9772,0.9503,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.7333,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.8916,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0026,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9909,0.0075,0.0004,0.0002</t>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9777,0.0309,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9992,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0021,0.0000,0.0000</t>
+    <t>0.0010,0.0012,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0117,0.0024,0.9894,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0001,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0000,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0084,0.9897,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.0073,0.9858,0.0098,0.0003</t>
+  </si>
+  <si>
+    <t>0.0053,0.9941,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0159,0.9829,0.0044,0.0004</t>
+  </si>
+  <si>
+    <t>0.0015,0.9968,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.7198,0.4053,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.1389,0.0064,0.7836,0.0019</t>
+  </si>
+  <si>
+    <t>0.0902,0.0003,0.9495,0.0002</t>
+  </si>
+  <si>
+    <t>0.0542,0.0157,0.7469,0.0090</t>
+  </si>
+  <si>
+    <t>0.0800,0.0046,0.9161,0.0009</t>
+  </si>
+  <si>
+    <t>0.0183,0.5609,0.0211,0.5604</t>
+  </si>
+  <si>
+    <t>0.0052,0.9874,0.0091,0.0007</t>
+  </si>
+  <si>
+    <t>0.0003,0.9988,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9951,0.9205,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9979,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.4710,0.5575,0.0097,0.0020</t>
+  </si>
+  <si>
+    <t>0.3942,0.6160,0.0172,0.0012</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9695,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9911,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.7508,0.9962,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.1248,0.9877,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0000,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.7280,0.0003,0.3243,0.0002</t>
+  </si>
+  <si>
+    <t>0.3633,0.0000,0.8809,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0001,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.8290,0.0025,0.0030,0.1479</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9954,0.9958,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0076,0.0018,0.9928,0.0001</t>
-  </si>
-  <si>
-    <t>0.9635,0.0003,0.0318,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0003,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.9926,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.0197,0.9783,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.9988,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9969,0.0110,0.0001</t>
-  </si>
-  <si>
-    <t>0.8486,0.1957,0.0036,0.0002</t>
-  </si>
-  <si>
-    <t>0.8330,0.0075,0.0983,0.0004</t>
-  </si>
-  <si>
-    <t>0.9658,0.0010,0.0202,0.0001</t>
-  </si>
-  <si>
-    <t>0.0445,0.0038,0.9207,0.0019</t>
-  </si>
-  <si>
-    <t>0.2931,0.0007,0.7995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0080,0.5643,0.0171,0.7558</t>
-  </si>
-  <si>
-    <t>0.0027,0.9940,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.0005,0.9984,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9967,0.8281,0.0000</t>
-  </si>
-  <si>
-    <t>0.0039,0.9945,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.8980,0.1014,0.0091,0.0030</t>
-  </si>
-  <si>
-    <t>0.3586,0.6879,0.0044,0.0020</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0011,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9558,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8756,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.2567,0.9475,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0097,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.9955,0.0002,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.5570,0.0010,0.3472,0.0008</t>
-  </si>
-  <si>
-    <t>0.0457,0.0001,0.9843,0.0000</t>
-  </si>
-  <si>
-    <t>0.9425,0.0004,0.0560,0.0001</t>
-  </si>
-  <si>
-    <t>0.0348,0.0006,0.0002,0.9880</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0003,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.9190,0.0932,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1139,0.9123,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.9952,0.0003,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.4558,0.0001,0.0045,0.4716</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0101,0.9963,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.7116,0.1900,0.0183,0.0004</t>
-  </si>
-  <si>
-    <t>0.9956,0.0017,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9950,0.0015,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0457,0.9224,0.0126,0.0014</t>
-  </si>
-  <si>
-    <t>0.8727,0.0370,0.0391,0.0019</t>
-  </si>
-  <si>
-    <t>0.9958,0.0016,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0001</t>
+    <t>0.1451,0.8829,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.8102,0.2165,0.0031,0.0005</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8320,0.0000,0.0012,0.1018</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0024,0.9944,0.0008</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.3288,0.1813,0.1090,0.0008</t>
+  </si>
+  <si>
+    <t>0.9905,0.0062,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9437,0.0237,0.0089,0.0005</t>
+  </si>
+  <si>
+    <t>0.0278,0.9597,0.0049,0.0011</t>
+  </si>
+  <si>
+    <t>0.8759,0.0185,0.0586,0.0011</t>
+  </si>
+  <si>
+    <t>0.9947,0.0039,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0003</t>
   </si>
   <si>
     <t>0.9993,0.0002,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9992,0.0001,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.1829,0.8509,0.0037,0.0005</t>
-  </si>
-  <si>
-    <t>0.8492,0.1653,0.0056,0.0002</t>
-  </si>
-  <si>
-    <t>0.9838,0.0210,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0084,0.0499,0.9817,0.0012</t>
-  </si>
-  <si>
-    <t>0.9931,0.0048,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0011,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9232,0.0640,0.0124,0.0052</t>
-  </si>
-  <si>
-    <t>0.0000,0.0114,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.8288,0.0224,0.0925,0.0175</t>
-  </si>
-  <si>
-    <t>0.0000,0.0011,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0034,0.9991,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0914,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0009,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0034,0.0001,0.9954,0.0005</t>
-  </si>
-  <si>
-    <t>0.0175,0.0004,0.9907,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.0011,0.9919,0.0008</t>
-  </si>
-  <si>
-    <t>0.0211,0.4031,0.5260,0.0003</t>
-  </si>
-  <si>
-    <t>0.0095,0.0063,0.9821,0.0003</t>
-  </si>
-  <si>
-    <t>0.9206,0.0010,0.0541,0.0001</t>
-  </si>
-  <si>
-    <t>0.8458,0.0044,0.0827,0.0018</t>
-  </si>
-  <si>
-    <t>0.0076,0.0004,0.9925,0.0009</t>
-  </si>
-  <si>
-    <t>0.0046,0.9958,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0056,0.9954,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.8339,0.2607,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.5119,0.6030,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.0022,0.9977,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9034,0.0062,0.0573,0.0001</t>
-  </si>
-  <si>
-    <t>0.9947,0.0001,0.0030,0.0000</t>
-  </si>
-  <si>
-    <t>0.9918,0.0009,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.7269,0.0054,0.2650,0.0004</t>
-  </si>
-  <si>
-    <t>0.9103,0.0012,0.0580,0.0002</t>
-  </si>
-  <si>
-    <t>0.0016,0.0003,0.9954,0.0040</t>
-  </si>
-  <si>
-    <t>0.0022,0.1609,0.9847,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0304,0.9972,0.0001</t>
-  </si>
-  <si>
-    <t>0.0087,0.0015,0.9943,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0996,0.9954,0.0000</t>
-  </si>
-  <si>
-    <t>0.9959,0.0001,0.0000,0.0026</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9967,0.0010,0.0000,0.0003</t>
+    <t>0.9984,0.0007,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0000,0.0000,0.0010</t>
+  </si>
+  <si>
+    <t>0.8491,0.2445,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9818,0.0167,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.5573,0.5753,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.3083,0.0414,0.7158,0.0023</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9962,0.0008,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.7994,0.1311,0.0525,0.0035</t>
+  </si>
+  <si>
+    <t>0.0001,0.0014,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9422,0.0258,0.0202,0.0040</t>
+  </si>
+  <si>
+    <t>0.0000,0.0010,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0356,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.1302,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0008,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9990,0.0003</t>
+  </si>
+  <si>
+    <t>0.1654,0.0018,0.8951,0.0000</t>
+  </si>
+  <si>
+    <t>0.5131,0.0014,0.4689,0.0005</t>
+  </si>
+  <si>
+    <t>0.0134,0.0029,0.9789,0.0002</t>
+  </si>
+  <si>
+    <t>0.0120,0.0036,0.9754,0.0004</t>
+  </si>
+  <si>
+    <t>0.7343,0.0028,0.2894,0.0003</t>
+  </si>
+  <si>
+    <t>0.9223,0.0027,0.0354,0.0008</t>
+  </si>
+  <si>
+    <t>0.3938,0.0016,0.7182,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.9970,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0070,0.9946,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.7166,0.4474,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.2440,0.8485,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0025,0.9973,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9705,0.0043,0.0076,0.0001</t>
+  </si>
+  <si>
+    <t>0.9936,0.0000,0.0065,0.0000</t>
+  </si>
+  <si>
+    <t>0.9336,0.0059,0.0228,0.0025</t>
+  </si>
+  <si>
+    <t>0.9360,0.0009,0.0612,0.0000</t>
+  </si>
+  <si>
+    <t>0.4692,0.0007,0.5115,0.0007</t>
+  </si>
+  <si>
+    <t>0.0016,0.0003,0.9964,0.0025</t>
+  </si>
+  <si>
+    <t>0.0021,0.0749,0.9874,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0532,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0020,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.8141,0.6646,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9823,0.0051,0.0000,0.0009</t>
+  </si>
+  <si>
+    <t>0.9920,0.0074,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9911,0.0066,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0016,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0007,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0573,0.0596,0.7119,0.0041</t>
+  </si>
+  <si>
+    <t>0.9767,0.0006,0.0089,0.0002</t>
+  </si>
+  <si>
+    <t>0.0029,0.0001,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0015,0.9993,0.0003</t>
+  </si>
+  <si>
+    <t>0.0030,0.3193,0.9558,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0015,0.9974,0.0008</t>
+  </si>
+  <si>
+    <t>0.9740,0.0002,0.0185,0.0000</t>
+  </si>
+  <si>
+    <t>0.2335,0.0000,0.8831,0.0001</t>
+  </si>
+  <si>
+    <t>0.9907,0.0004,0.0033,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9961,0.0041,0.0002,0.0001</t>
   </si>
   <si>
     <t>0.9995,0.0004,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9932,0.0038,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9978,0.0013,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0007,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0031,0.9989,0.0003</t>
-  </si>
-  <si>
-    <t>0.0204,0.2081,0.6196,0.0038</t>
-  </si>
-  <si>
-    <t>0.7974,0.0007,0.1568,0.0005</t>
-  </si>
-  <si>
-    <t>0.0008,0.0003,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0074,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.4227,0.9717,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0012,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0009,0.9985,0.0005</t>
-  </si>
-  <si>
-    <t>0.9648,0.0004,0.0214,0.0002</t>
-  </si>
-  <si>
-    <t>0.9506,0.0002,0.0488,0.0000</t>
-  </si>
-  <si>
-    <t>0.9895,0.0006,0.0036,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0014,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9986,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9960,0.0037,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0013,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0009,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.0189,0.9911,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.4341,0.9891,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0158,0.9917,0.0006</t>
-  </si>
-  <si>
-    <t>0.0015,0.0012,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0103,0.0035,0.9837,0.0013</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0083,0.0008,0.9870,0.0005</t>
-  </si>
-  <si>
-    <t>0.9210,0.0001,0.0025,0.0238</t>
-  </si>
-  <si>
-    <t>0.1055,0.0479,0.0004,0.8770</t>
-  </si>
-  <si>
-    <t>0.0332,0.0029,0.0034,0.9761</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9957,0.0005,0.0009,0.0002</t>
+    <t>0.9979,0.0016,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.0066,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.5506,0.9892,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0394,0.9869,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.0011,0.9966,0.0000</t>
+  </si>
+  <si>
+    <t>0.0066,0.0012,0.9898,0.0010</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.0028,0.9964,0.0002</t>
+  </si>
+  <si>
+    <t>0.9924,0.0003,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.0165,0.0877,0.0003,0.9810</t>
+  </si>
+  <si>
+    <t>0.0498,0.0005,0.0020,0.9736</t>
+  </si>
+  <si>
+    <t>0.9962,0.0010,0.0004,0.0003</t>
   </si>
 </sst>
 </file>
@@ -1893,7 +1893,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1907,7 +1907,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1921,7 +1921,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1935,7 +1935,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1949,7 +1949,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1963,7 +1963,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1977,7 +1977,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1991,7 +1991,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2005,7 +2005,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2019,7 +2019,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2033,7 +2033,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2047,7 +2047,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2464,7 +2464,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>304</v>
@@ -2506,7 +2506,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
         <v>307</v>
@@ -2576,7 +2576,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
         <v>312</v>
@@ -2898,7 +2898,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>335</v>
@@ -2940,7 +2940,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D77" t="s">
         <v>338</v>
@@ -3111,7 +3111,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3153,7 +3153,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>274</v>
+        <v>352</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3167,7 +3167,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3181,7 +3181,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>274</v>
+        <v>354</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3195,7 +3195,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3209,7 +3209,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3223,7 +3223,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>356</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3237,7 +3237,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>357</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3251,7 +3251,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3265,7 +3265,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3279,7 +3279,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3293,7 +3293,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3307,7 +3307,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3321,7 +3321,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3335,7 +3335,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3349,7 +3349,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3363,7 +3363,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3377,7 +3377,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3391,7 +3391,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3405,7 +3405,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3419,7 +3419,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3433,7 +3433,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3447,7 +3447,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3461,7 +3461,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3475,7 +3475,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3486,10 +3486,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3500,10 +3500,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3517,7 +3517,7 @@
         <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3531,7 +3531,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3545,7 +3545,7 @@
         <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3559,7 +3559,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3573,7 +3573,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3587,7 +3587,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3601,7 +3601,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3615,7 +3615,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3626,10 +3626,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3643,7 +3643,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3657,7 +3657,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>274</v>
+        <v>382</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3671,7 +3671,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3685,7 +3685,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>273</v>
+        <v>384</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3699,7 +3699,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3713,7 +3713,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3727,7 +3727,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3741,7 +3741,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3755,7 +3755,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3769,7 +3769,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3783,7 +3783,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3794,10 +3794,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3811,7 +3811,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3825,7 +3825,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3839,7 +3839,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3853,7 +3853,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3867,7 +3867,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3878,10 +3878,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D144" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3895,7 +3895,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3909,7 +3909,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3923,7 +3923,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3937,7 +3937,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3951,7 +3951,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>355</v>
+        <v>400</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3962,10 +3962,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3979,7 +3979,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>398</v>
+        <v>356</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3990,10 +3990,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4007,7 +4007,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4021,7 +4021,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4035,7 +4035,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4049,7 +4049,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4063,7 +4063,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4077,7 +4077,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4088,10 +4088,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D159" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4105,7 +4105,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4119,7 +4119,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4133,7 +4133,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4147,7 +4147,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4161,7 +4161,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4175,7 +4175,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4189,7 +4189,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4203,7 +4203,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4217,7 +4217,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4231,7 +4231,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>415</v>
+        <v>358</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4245,7 +4245,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4259,7 +4259,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4273,7 +4273,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4284,10 +4284,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4301,7 +4301,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4312,10 +4312,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4329,7 +4329,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4343,7 +4343,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4357,7 +4357,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4371,7 +4371,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4385,7 +4385,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4399,7 +4399,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4413,7 +4413,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4427,7 +4427,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4441,7 +4441,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4455,7 +4455,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4469,7 +4469,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4483,7 +4483,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4497,7 +4497,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4511,7 +4511,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4525,7 +4525,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4539,7 +4539,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4550,10 +4550,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4567,7 +4567,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4581,7 +4581,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4595,7 +4595,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4609,7 +4609,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4623,7 +4623,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4637,7 +4637,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4651,7 +4651,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4665,7 +4665,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4679,7 +4679,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4693,7 +4693,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4707,7 +4707,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4721,7 +4721,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4735,7 +4735,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4749,7 +4749,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4760,10 +4760,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4777,7 +4777,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4791,7 +4791,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4805,7 +4805,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4819,7 +4819,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4830,10 +4830,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4847,7 +4847,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>458</v>
+        <v>272</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4861,7 +4861,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4875,7 +4875,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4889,7 +4889,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4903,7 +4903,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4917,7 +4917,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4931,7 +4931,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4945,7 +4945,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>402</v>
+        <v>358</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4959,7 +4959,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4973,7 +4973,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4987,7 +4987,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5001,7 +5001,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5015,7 +5015,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5029,7 +5029,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5043,7 +5043,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5057,7 +5057,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5071,7 +5071,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5085,7 +5085,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5099,7 +5099,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5113,7 +5113,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5124,10 +5124,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5141,7 +5141,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5155,7 +5155,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5169,7 +5169,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5183,7 +5183,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>269</v>
+        <v>358</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5197,7 +5197,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5211,7 +5211,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>274</v>
+        <v>358</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5225,7 +5225,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5239,7 +5239,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5253,7 +5253,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5267,7 +5267,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5278,10 +5278,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D244" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5295,7 +5295,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5309,7 +5309,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5323,7 +5323,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5337,7 +5337,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5351,7 +5351,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5365,7 +5365,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5379,7 +5379,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5393,7 +5393,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5407,7 +5407,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5421,7 +5421,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>496</v>
+        <v>396</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5435,7 +5435,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="256" spans="1:4">
